--- a/parser/data/xlsx/user_input.xlsx
+++ b/parser/data/xlsx/user_input.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:56:42.240309</t>
+          <t>2026-02-25T17:23:29.067738</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/user_input.xlsx
+++ b/parser/data/xlsx/user_input.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T17:23:29.067738</t>
+          <t>2026-02-25T18:04:17.627959</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/user_input.xlsx
+++ b/parser/data/xlsx/user_input.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T18:04:17.627959</t>
+          <t>2026-02-26T13:48:49.142831</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/user_input.xlsx
+++ b/parser/data/xlsx/user_input.xlsx
@@ -417,7 +417,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T13:48:49.142831</t>
+          <t>2026-02-26T14:46:10.060418</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>data.csv</t>
+          <t>7abc486a8f2944fab510c38389cbf6f4.csv</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\churn\data.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\7abc486a8f2944fab510c38389cbf6f4.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/user_input.xlsx
+++ b/parser/data/xlsx/user_input.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T14:46:10.060418</t>
+          <t>2026-02-26T14:55:24.019397</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7abc486a8f2944fab510c38389cbf6f4.csv</t>
+          <t>5a6b5300428640cbaae38090de224504.csv</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\7abc486a8f2944fab510c38389cbf6f4.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\5a6b5300428640cbaae38090de224504.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/user_input.xlsx
+++ b/parser/data/xlsx/user_input.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="record_1_metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="record_2_metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="record_3_metadata" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,4 +473,136 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="113" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:08:33.195373</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dataset_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>data.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\traffic_violations_100k\data.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:12:58.223518</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dataset_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>42d1e5bfc1a9434c8980fd2b57f3f8d8.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\42d1e5bfc1a9434c8980fd2b57f3f8d8.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>